--- a/Abgabe/Aufgabe 1/Visualization.xlsx
+++ b/Abgabe/Aufgabe 1/Visualization.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/bc22b3beb6a9d410/Dokumente (OneDrive)/00_Uni/Master/02_Module/2. Semester/Alda/Lab_AlDa/Abgabe/Aufgabe 1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="9" documentId="8_{11561085-90A8-4B92-BF97-EB6D5CA12764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{34AF94E1-E23D-4FAF-B463-5BC27709B153}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{11561085-90A8-4B92-BF97-EB6D5CA12764}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D547D312-763F-444D-A6E9-F5AD17DC9F3D}"/>
   <bookViews>
-    <workbookView xWindow="1740" yWindow="2415" windowWidth="28800" windowHeight="15345" xr2:uid="{860E5B01-685A-4F28-A739-064A4CCB5B7D}"/>
+    <workbookView minimized="1" xWindow="3735" yWindow="2775" windowWidth="23370" windowHeight="15345" xr2:uid="{860E5B01-685A-4F28-A739-064A4CCB5B7D}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -52,7 +52,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="168" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="0.00000"/>
   </numFmts>
   <fonts count="1" x14ac:knownFonts="1">
     <font>
@@ -86,7 +86,7 @@
   <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -97,7 +97,7 @@
       <numFmt numFmtId="14" formatCode="0.00%"/>
     </dxf>
     <dxf>
-      <numFmt numFmtId="168" formatCode="0.00000"/>
+      <numFmt numFmtId="164" formatCode="0.00000"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="3" formatCode="#,##0"/>
@@ -998,10 +998,10 @@
       <xdr:rowOff>61912</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>238125</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>138112</xdr:rowOff>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>352425</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>38100</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1027,6 +1027,10 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1435,6 +1439,22 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{05C60535-1F16-4fd2-B633-F4F36F0B64E0}">
       <x14:sparklineGroups xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
+        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{244D215F-78F9-4E87-8E99-362521E2A217}">
+          <x14:colorSeries rgb="FF376092"/>
+          <x14:colorNegative rgb="FFD00000"/>
+          <x14:colorAxis rgb="FF000000"/>
+          <x14:colorMarkers rgb="FFD00000"/>
+          <x14:colorFirst rgb="FFD00000"/>
+          <x14:colorLast rgb="FFD00000"/>
+          <x14:colorHigh rgb="FFD00000"/>
+          <x14:colorLow rgb="FFD00000"/>
+          <x14:sparklines>
+            <x14:sparkline>
+              <xm:f>Tabelle1!B4:B4</xm:f>
+              <xm:sqref>K11</xm:sqref>
+            </x14:sparkline>
+          </x14:sparklines>
+        </x14:sparklineGroup>
         <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{5C936622-0765-4DD1-8601-E16391FD4EF8}">
           <x14:colorSeries rgb="FF376092"/>
           <x14:colorNegative rgb="FFD00000"/>
@@ -1451,22 +1471,6 @@
             </x14:sparkline>
           </x14:sparklines>
         </x14:sparklineGroup>
-        <x14:sparklineGroup displayEmptyCellsAs="gap" xr2:uid="{244D215F-78F9-4E87-8E99-362521E2A217}">
-          <x14:colorSeries rgb="FF376092"/>
-          <x14:colorNegative rgb="FFD00000"/>
-          <x14:colorAxis rgb="FF000000"/>
-          <x14:colorMarkers rgb="FFD00000"/>
-          <x14:colorFirst rgb="FFD00000"/>
-          <x14:colorLast rgb="FFD00000"/>
-          <x14:colorHigh rgb="FFD00000"/>
-          <x14:colorLow rgb="FFD00000"/>
-          <x14:sparklines>
-            <x14:sparkline>
-              <xm:f>Tabelle1!B4:B4</xm:f>
-              <xm:sqref>K11</xm:sqref>
-            </x14:sparkline>
-          </x14:sparklines>
-        </x14:sparklineGroup>
       </x14:sparklineGroups>
     </ext>
   </extLst>
